--- a/stories/arbres/TREE-DIF-026.xlsx
+++ b/stories/arbres/TREE-DIF-026.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Zoé est avec maman, dans la cuisine. Zoé a envie de jouer. maman est là, tout près. On va apprendre : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Zoé écoute maman. Zoé entend les mots : pas rire de l'apparence.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1538,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Zoé va vers le bac à sable. Un chat miaule une fois. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Zoé se souvient : pas rire de l'apparence. Voici le geste : jouer ; pas rire. On range un objet. maman dit : je suis là. On reste ensemble.</t>
+          <t>Zoé va vers le bac à sable. Un chat miaule une fois. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Zoé se souvient : pas rire de l'apparence. Voici le geste : jouer ; pas rire. On range un objet. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1649,6 +1676,12 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé va vers le bac à sable. Un chat miaule une fois. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Zoé se souvient : pas rire de l'apparence. Voici le geste : jouer ; pas rire. On range un objet.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1858,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Lunettes, cheveux, habit.</t>
         </is>
       </c>
     </row>
@@ -1993,6 +2031,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : jouer ; pas rire. Zoé respire. Zoé retient : pas rire de l'apparence. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2179,6 +2222,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2341,6 +2389,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé a choisi le ballon. La couverture est douce. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : jouer ; pas rire. Zoé répète tout bas : pas rire de l'apparence. On écoute jusqu'au bout. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2529,6 +2582,11 @@
       <c r="AV9" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -2693,6 +2751,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint Tom. Le vent est doux. On range un objet. Cette fin-là est celle de le bac à sable, le ballon et Tom. Zoé a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Zoé a entendu : pas rire de l'apparence. Zoé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2855,6 +2918,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3017,6 +3085,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint Léa. Le sol est un peu froid. On dit merci. Cette fin-là est celle de le bac à sable, le ballon et Léa. Zoé a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Zoé a entendu : pas rire de l'apparence. Zoé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3179,6 +3252,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3341,6 +3419,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint Sami. Une feuille tombe. On souffle doucement. Cette fin-là est celle de le bac à sable, le ballon et Sami. Zoé a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Zoé a entendu : pas rire de l'apparence. Zoé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3503,6 +3586,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3665,6 +3753,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé a choisi le seau. On entend un oiseau. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : jouer ; pas rire. Zoé répète tout bas : pas rire de l'apparence. On attend son tour. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3853,6 +3946,11 @@
       <c r="AV17" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -4017,6 +4115,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint Tom. Le sol est un peu froid. On range un objet. Cette fin-là est celle de le bac à sable, le seau et Tom. Zoé a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Zoé a entendu : pas rire de l'apparence. Zoé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4179,6 +4282,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4341,6 +4449,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint Léa. Une feuille tombe. On dit merci. Cette fin-là est celle de le bac à sable, le seau et Léa. Zoé a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Zoé a entendu : pas rire de l'apparence. Zoé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4503,6 +4616,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4665,6 +4783,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint Sami. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de le bac à sable, le seau et Sami. Zoé a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Zoé a entendu : pas rire de l'apparence. Zoé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4827,6 +4950,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4989,6 +5117,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé a choisi le doudou. Ça sent le pain chaud. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : jouer ; pas rire. Zoé répète tout bas : pas rire de l'apparence. On montre du doigt, sans courir. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5177,6 +5310,11 @@
       <c r="AV25" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -5341,6 +5479,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint Tom. Une feuille tombe. On range un objet. Cette fin-là est celle de le bac à sable, le doudou et Tom. Zoé a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Zoé a entendu : pas rire de l'apparence. Zoé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5503,6 +5646,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5665,6 +5813,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint Léa. L'eau coule, tout petit bruit. On dit merci. Cette fin-là est celle de le bac à sable, le doudou et Léa. Zoé a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Zoé a entendu : pas rire de l'apparence. Zoé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5827,6 +5980,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5989,6 +6147,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint Sami. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de le bac à sable, le doudou et Sami. Zoé a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Zoé a entendu : pas rire de l'apparence. Zoé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6151,6 +6314,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6175,7 +6343,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Zoé va vers le toboggan. Les chaussures font toc toc. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Zoé se souvient : pas rire de l'apparence. Voici le geste : jouer ; pas rire. On dit merci. maman dit : je suis là. On reste ensemble.</t>
+          <t>Zoé va vers le toboggan. Les chaussures font toc toc. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Zoé se souvient : pas rire de l'apparence. Voici le geste : jouer ; pas rire. On dit merci. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6313,6 +6481,12 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé va vers le toboggan. Les chaussures font toc toc. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Zoé se souvient : pas rire de l'apparence. Voici le geste : jouer ; pas rire. On dit merci.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6489,6 +6663,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Lunettes, cheveux, habit.</t>
         </is>
       </c>
     </row>
@@ -6657,6 +6836,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : jouer ; pas rire. Zoé respire. Zoé retient : pas rire de l'apparence. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6843,6 +7027,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7005,6 +7194,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé a choisi le ballon. Le vent est doux. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : jouer ; pas rire. Zoé répète tout bas : pas rire de l'apparence. On écoute jusqu'au bout. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7193,6 +7387,11 @@
       <c r="AV37" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -7357,6 +7556,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint Tom. Le sol est un peu froid. On dit merci. Cette fin-là est celle de le toboggan, le ballon et Tom. Zoé a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Zoé a entendu : pas rire de l'apparence. Zoé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7519,6 +7723,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7681,6 +7890,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint Léa. Une feuille tombe. On souffle doucement. Cette fin-là est celle de le toboggan, le ballon et Léa. Zoé a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Zoé a entendu : pas rire de l'apparence. Zoé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7843,6 +8057,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8005,6 +8224,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint Sami. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le ballon et Sami. Zoé a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Zoé a entendu : pas rire de l'apparence. Zoé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8167,6 +8391,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8329,6 +8558,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé a choisi le seau. Le sol est un peu froid. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : jouer ; pas rire. Zoé répète tout bas : pas rire de l'apparence. On attend son tour. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8517,6 +8751,11 @@
       <c r="AV45" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -8681,6 +8920,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint Tom. Une feuille tombe. On dit merci. Cette fin-là est celle de le toboggan, le seau et Tom. Zoé a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Zoé a entendu : pas rire de l'apparence. Zoé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8843,6 +9087,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9005,6 +9254,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint Léa. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de le toboggan, le seau et Léa. Zoé a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Zoé a entendu : pas rire de l'apparence. Zoé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9167,6 +9421,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9329,6 +9588,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint Sami. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le seau et Sami. Zoé a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Zoé a entendu : pas rire de l'apparence. Zoé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9491,6 +9755,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9653,6 +9922,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé a choisi le doudou. Une feuille tombe. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : jouer ; pas rire. Zoé répète tout bas : pas rire de l'apparence. On montre du doigt, sans courir. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9841,6 +10115,11 @@
       <c r="AV53" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -10005,6 +10284,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint Tom. L'eau coule, tout petit bruit. On dit merci. Cette fin-là est celle de le toboggan, le doudou et Tom. Zoé a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Zoé a entendu : pas rire de l'apparence. Zoé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10167,6 +10451,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10329,6 +10618,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint Léa. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de le toboggan, le doudou et Léa. Zoé a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Zoé a entendu : pas rire de l'apparence. Zoé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10491,6 +10785,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10653,6 +10952,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint Sami. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le doudou et Sami. Zoé a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Zoé a entendu : pas rire de l'apparence. Zoé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10815,6 +11119,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10839,7 +11148,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Zoé va vers les balançoires. La couverture est douce. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Zoé se souvient : pas rire de l'apparence. Voici le geste : jouer ; pas rire. On souffle doucement. maman dit : je suis là. On reste ensemble.</t>
+          <t>Zoé va vers les balançoires. La couverture est douce. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Zoé se souvient : pas rire de l'apparence. Voici le geste : jouer ; pas rire. On souffle doucement. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10977,6 +11286,12 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé va vers les balançoires. La couverture est douce. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Zoé se souvient : pas rire de l'apparence. Voici le geste : jouer ; pas rire. On souffle doucement.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11153,6 +11468,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Lunettes, cheveux, habit.</t>
         </is>
       </c>
     </row>
@@ -11321,6 +11641,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : jouer ; pas rire. Zoé respire. Zoé retient : pas rire de l'apparence. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11507,6 +11832,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11669,6 +11999,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé a choisi le ballon. L'eau coule, tout petit bruit. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : jouer ; pas rire. Zoé répète tout bas : pas rire de l'apparence. On écoute jusqu'au bout. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11857,6 +12192,11 @@
       <c r="AV65" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -12021,6 +12361,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint Tom. Une feuille tombe. On souffle doucement. Cette fin-là est celle de les balançoires, le ballon et Tom. Zoé a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Zoé a entendu : pas rire de l'apparence. Zoé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12183,6 +12528,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12345,6 +12695,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint Léa. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le ballon et Léa. Zoé a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Zoé a entendu : pas rire de l'apparence. Zoé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12507,6 +12862,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12669,6 +13029,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint Sami. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de les balançoires, le ballon et Sami. Zoé a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Zoé a entendu : pas rire de l'apparence. Zoé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12831,6 +13196,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12993,6 +13363,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé a choisi le seau. Un vélo passe au loin. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : jouer ; pas rire. Zoé répète tout bas : pas rire de l'apparence. On attend son tour. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13181,6 +13556,11 @@
       <c r="AV73" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -13345,6 +13725,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint Tom. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de les balançoires, le seau et Tom. Zoé a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Zoé a entendu : pas rire de l'apparence. Zoé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13507,6 +13892,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13669,6 +14059,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint Léa. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le seau et Léa. Zoé a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Zoé a entendu : pas rire de l'apparence. Zoé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13831,6 +14226,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13993,6 +14393,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint Sami. La lumière est claire. On attend son tour. Cette fin-là est celle de les balançoires, le seau et Sami. Zoé a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Zoé a entendu : pas rire de l'apparence. Zoé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14155,6 +14560,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14317,6 +14727,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé a choisi le doudou. La lumière est claire. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : jouer ; pas rire. Zoé répète tout bas : pas rire de l'apparence. On montre du doigt, sans courir. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14505,6 +14920,11 @@
       <c r="AV81" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -14669,6 +15089,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint Tom. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de les balançoires, le doudou et Tom. Zoé a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Zoé a entendu : pas rire de l'apparence. Zoé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14831,6 +15256,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14993,6 +15423,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint Léa. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le doudou et Léa. Zoé a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Zoé a entendu : pas rire de l'apparence. Zoé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15155,6 +15590,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15317,6 +15757,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint Sami. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de les balançoires, le doudou et Sami. Zoé a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Zoé a entendu : pas rire de l'apparence. Zoé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15479,6 +15924,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15497,7 +15947,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15570,6 +16020,13 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>ch3C3: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-DIF-026.xlsx
+++ b/stories/arbres/TREE-DIF-026.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Aujourd'hui, Zoé est avec maman, dans la cuisine. Zoé a envie de jouer. maman est là, tout près. On va apprendre : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Zoé écoute maman. Zoé entend les mots : pas rire de l'apparence.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1520,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1682,6 +1689,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1865,6 +1873,7 @@
           <t>narrateur|Que fait-on ? Lunettes, cheveux, habit.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2036,6 +2045,7 @@
           <t>narrateur|Oui. Voici le geste : jouer ; pas rire. Zoé respire. Zoé retient : pas rire de l'apparence. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2227,6 +2237,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2394,6 +2405,7 @@
           <t>narrateur|Zoé a choisi le ballon. La couverture est douce. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : jouer ; pas rire. Zoé répète tout bas : pas rire de l'apparence. On écoute jusqu'au bout. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2589,6 +2601,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2756,6 +2769,7 @@
           <t>narrateur|Zoé rejoint Tom. Le vent est doux. On range un objet. Cette fin-là est celle de le bac à sable, le ballon et Tom. Zoé a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Zoé a entendu : pas rire de l'apparence. Zoé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2923,6 +2937,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3090,6 +3105,7 @@
           <t>narrateur|Zoé rejoint Léa. Le sol est un peu froid. On dit merci. Cette fin-là est celle de le bac à sable, le ballon et Léa. Zoé a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Zoé a entendu : pas rire de l'apparence. Zoé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3257,6 +3273,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3424,6 +3441,7 @@
           <t>narrateur|Zoé rejoint Sami. Une feuille tombe. On souffle doucement. Cette fin-là est celle de le bac à sable, le ballon et Sami. Zoé a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Zoé a entendu : pas rire de l'apparence. Zoé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3591,6 +3609,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3758,6 +3777,7 @@
           <t>narrateur|Zoé a choisi le seau. On entend un oiseau. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : jouer ; pas rire. Zoé répète tout bas : pas rire de l'apparence. On attend son tour. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3953,6 +3973,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4120,6 +4141,7 @@
           <t>narrateur|Zoé rejoint Tom. Le sol est un peu froid. On range un objet. Cette fin-là est celle de le bac à sable, le seau et Tom. Zoé a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Zoé a entendu : pas rire de l'apparence. Zoé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4287,6 +4309,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4454,6 +4477,7 @@
           <t>narrateur|Zoé rejoint Léa. Une feuille tombe. On dit merci. Cette fin-là est celle de le bac à sable, le seau et Léa. Zoé a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Zoé a entendu : pas rire de l'apparence. Zoé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4621,6 +4645,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4788,6 +4813,7 @@
           <t>narrateur|Zoé rejoint Sami. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de le bac à sable, le seau et Sami. Zoé a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Zoé a entendu : pas rire de l'apparence. Zoé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4955,6 +4981,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5122,6 +5149,7 @@
           <t>narrateur|Zoé a choisi le doudou. Ça sent le pain chaud. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : jouer ; pas rire. Zoé répète tout bas : pas rire de l'apparence. On montre du doigt, sans courir. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5317,6 +5345,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5484,6 +5513,7 @@
           <t>narrateur|Zoé rejoint Tom. Une feuille tombe. On range un objet. Cette fin-là est celle de le bac à sable, le doudou et Tom. Zoé a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Zoé a entendu : pas rire de l'apparence. Zoé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5651,6 +5681,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5818,6 +5849,7 @@
           <t>narrateur|Zoé rejoint Léa. L'eau coule, tout petit bruit. On dit merci. Cette fin-là est celle de le bac à sable, le doudou et Léa. Zoé a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Zoé a entendu : pas rire de l'apparence. Zoé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5985,6 +6017,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6152,6 +6185,7 @@
           <t>narrateur|Zoé rejoint Sami. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de le bac à sable, le doudou et Sami. Zoé a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Zoé a entendu : pas rire de l'apparence. Zoé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6319,6 +6353,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6487,6 +6522,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6670,6 +6706,7 @@
           <t>narrateur|Que fait-on ? Lunettes, cheveux, habit.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6841,6 +6878,7 @@
           <t>narrateur|Oui. Voici le geste : jouer ; pas rire. Zoé respire. Zoé retient : pas rire de l'apparence. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7032,6 +7070,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7199,6 +7238,7 @@
           <t>narrateur|Zoé a choisi le ballon. Le vent est doux. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : jouer ; pas rire. Zoé répète tout bas : pas rire de l'apparence. On écoute jusqu'au bout. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7394,6 +7434,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7561,6 +7602,7 @@
           <t>narrateur|Zoé rejoint Tom. Le sol est un peu froid. On dit merci. Cette fin-là est celle de le toboggan, le ballon et Tom. Zoé a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Zoé a entendu : pas rire de l'apparence. Zoé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7728,6 +7770,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7895,6 +7938,7 @@
           <t>narrateur|Zoé rejoint Léa. Une feuille tombe. On souffle doucement. Cette fin-là est celle de le toboggan, le ballon et Léa. Zoé a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Zoé a entendu : pas rire de l'apparence. Zoé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8062,6 +8106,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8229,6 +8274,7 @@
           <t>narrateur|Zoé rejoint Sami. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le ballon et Sami. Zoé a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Zoé a entendu : pas rire de l'apparence. Zoé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8396,6 +8442,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8563,6 +8610,7 @@
           <t>narrateur|Zoé a choisi le seau. Le sol est un peu froid. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : jouer ; pas rire. Zoé répète tout bas : pas rire de l'apparence. On attend son tour. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8758,6 +8806,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8925,6 +8974,7 @@
           <t>narrateur|Zoé rejoint Tom. Une feuille tombe. On dit merci. Cette fin-là est celle de le toboggan, le seau et Tom. Zoé a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Zoé a entendu : pas rire de l'apparence. Zoé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9092,6 +9142,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9259,6 +9310,7 @@
           <t>narrateur|Zoé rejoint Léa. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de le toboggan, le seau et Léa. Zoé a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Zoé a entendu : pas rire de l'apparence. Zoé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9426,6 +9478,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9593,6 +9646,7 @@
           <t>narrateur|Zoé rejoint Sami. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le seau et Sami. Zoé a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Zoé a entendu : pas rire de l'apparence. Zoé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9760,6 +9814,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9927,6 +9982,7 @@
           <t>narrateur|Zoé a choisi le doudou. Une feuille tombe. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : jouer ; pas rire. Zoé répète tout bas : pas rire de l'apparence. On montre du doigt, sans courir. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10122,6 +10178,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10289,6 +10346,7 @@
           <t>narrateur|Zoé rejoint Tom. L'eau coule, tout petit bruit. On dit merci. Cette fin-là est celle de le toboggan, le doudou et Tom. Zoé a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Zoé a entendu : pas rire de l'apparence. Zoé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10456,6 +10514,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10623,6 +10682,7 @@
           <t>narrateur|Zoé rejoint Léa. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de le toboggan, le doudou et Léa. Zoé a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Zoé a entendu : pas rire de l'apparence. Zoé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10790,6 +10850,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10957,6 +11018,7 @@
           <t>narrateur|Zoé rejoint Sami. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le doudou et Sami. Zoé a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Zoé a entendu : pas rire de l'apparence. Zoé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11124,6 +11186,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11292,6 +11355,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11475,6 +11539,7 @@
           <t>narrateur|Que fait-on ? Lunettes, cheveux, habit.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11646,6 +11711,7 @@
           <t>narrateur|Oui. Voici le geste : jouer ; pas rire. Zoé respire. Zoé retient : pas rire de l'apparence. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11837,6 +11903,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12004,6 +12071,7 @@
           <t>narrateur|Zoé a choisi le ballon. L'eau coule, tout petit bruit. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : jouer ; pas rire. Zoé répète tout bas : pas rire de l'apparence. On écoute jusqu'au bout. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12199,6 +12267,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12366,6 +12435,7 @@
           <t>narrateur|Zoé rejoint Tom. Une feuille tombe. On souffle doucement. Cette fin-là est celle de les balançoires, le ballon et Tom. Zoé a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Zoé a entendu : pas rire de l'apparence. Zoé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12533,6 +12603,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12700,6 +12771,7 @@
           <t>narrateur|Zoé rejoint Léa. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le ballon et Léa. Zoé a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Zoé a entendu : pas rire de l'apparence. Zoé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12867,6 +12939,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13034,6 +13107,7 @@
           <t>narrateur|Zoé rejoint Sami. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de les balançoires, le ballon et Sami. Zoé a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Zoé a entendu : pas rire de l'apparence. Zoé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13201,6 +13275,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13368,6 +13443,7 @@
           <t>narrateur|Zoé a choisi le seau. Un vélo passe au loin. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : jouer ; pas rire. Zoé répète tout bas : pas rire de l'apparence. On attend son tour. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13563,6 +13639,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13730,6 +13807,7 @@
           <t>narrateur|Zoé rejoint Tom. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de les balançoires, le seau et Tom. Zoé a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Zoé a entendu : pas rire de l'apparence. Zoé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13897,6 +13975,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14064,6 +14143,7 @@
           <t>narrateur|Zoé rejoint Léa. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le seau et Léa. Zoé a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Zoé a entendu : pas rire de l'apparence. Zoé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14231,6 +14311,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14398,6 +14479,7 @@
           <t>narrateur|Zoé rejoint Sami. La lumière est claire. On attend son tour. Cette fin-là est celle de les balançoires, le seau et Sami. Zoé a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Zoé a entendu : pas rire de l'apparence. Zoé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14565,6 +14647,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14732,6 +14815,7 @@
           <t>narrateur|Zoé a choisi le doudou. La lumière est claire. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : jouer ; pas rire. Zoé répète tout bas : pas rire de l'apparence. On montre du doigt, sans courir. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14927,6 +15011,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15094,6 +15179,7 @@
           <t>narrateur|Zoé rejoint Tom. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de les balançoires, le doudou et Tom. Zoé a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Zoé a entendu : pas rire de l'apparence. Zoé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15261,6 +15347,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15428,6 +15515,7 @@
           <t>narrateur|Zoé rejoint Léa. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le doudou et Léa. Zoé a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Zoé a entendu : pas rire de l'apparence. Zoé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15595,6 +15683,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15762,6 +15851,7 @@
           <t>narrateur|Zoé rejoint Sami. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de les balançoires, le doudou et Sami. Zoé a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Zoé a entendu : pas rire de l'apparence. Zoé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15929,6 +16019,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15947,7 +16038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16027,6 +16118,20 @@
       <c r="A11" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16041,7 +16146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16228,6 +16333,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/TREE-DIF-026.xlsx
+++ b/stories/arbres/TREE-DIF-026.xlsx
@@ -1378,12 +1378,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Trois affaires attendent près du coffre. Le drap, les pinces, et la marionnette. Tu prends quoi d'abord, Mila ?</t>
+          <t>Près du coffre, le drap sent encore le soleil. Les pinces cliquettent, la marionnette attend. Tu prends quoi d'abord, Mila ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Trois affaires attendent près du coffre. Le drap, les pinces, et la marionnette. Tu prends quoi d'abord, Mila ?</t>
+          <t>Près du coffre, le drap sent encore le soleil. Les pinces cliquettent, la marionnette attend. Tu prends quoi d'abord, Mila ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1542,8 +1542,8 @@
       <c r="AV3" s="2" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Trois affaires attendent près du coffre.
-narrateur|Le drap, les pinces, et la marionnette.
+          <t>narrateur|Près du coffre, le drap sent encore le soleil.
+narrateur|Les pinces cliquettent, la marionnette attend.
 maman|Tu prends quoi d'abord, Mila ?</t>
         </is>
       </c>
@@ -1571,12 +1571,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Mila prend d'abord le drap à carreaux. Il sent encore le soleil de la fenêtre. Glisse-le dans le panier, tout plié. Le tissu fait un petit froissement. Les pinces, ensuite, dans ta poche. Maman noue la marionnette rouge au poignet. Les trois affaires partent ensemble. Nino, tu portes le panier ? Je le tiens, même un peu flou. Le drap d'abord, vous l'avez.</t>
+          <t>Mila prend d'abord le drap à carreaux. Il sent encore le soleil de la fenêtre. Glisse-le dans le panier, tout plié. Le tissu fait un petit froissement. Les pinces, ensuite, dans ta poche. Maman noue la marionnette rouge au poignet. Tout le théâtre se met en route. Nino, tu portes le panier ? Je le tiens, même un peu flou. Le drap d'abord, vous l'avez.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Mila prend d'abord le drap à carreaux. Il sent encore le soleil de la fenêtre. Glisse-le dans le panier, tout plié. Le tissu fait un petit froissement. Les pinces, ensuite, dans ta poche. Maman noue la marionnette rouge au poignet. Les trois affaires partent ensemble. Nino, tu portes le panier ? Je le tiens, même un peu flou. Le drap d'abord, vous l'avez.</t>
+          <t>Mila prend d'abord le drap à carreaux. Il sent encore le soleil de la fenêtre. Glisse-le dans le panier, tout plié. Le tissu fait un petit froissement. Les pinces, ensuite, dans ta poche. Maman noue la marionnette rouge au poignet. Tout le théâtre se met en route. Nino, tu portes le panier ? Je le tiens, même un peu flou. Le drap d'abord, vous l'avez.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1717,7 +1717,7 @@
 narrateur|Le tissu fait un petit froissement.
 papa|Les pinces, ensuite, dans ta poche.
 narrateur|Maman noue la marionnette rouge au poignet.
-narrateur|Les trois affaires partent ensemble.
+narrateur|Tout le théâtre se met en route.
 enfant-f|Nino, tu portes le panier ?
 copain|Je le tiens, même un peu flou.
 papa|Le drap d'abord, vous l'avez.</t>
@@ -1747,12 +1747,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Mila a glissé le drap à carreaux dans le panier. C'est où, maintenant ?</t>
+          <t>Le drap à carreaux est dans le panier. Le drap est où ?</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Mila a glissé le drap à carreaux dans le panier. C'est où, maintenant ?</t>
+          <t>Le drap à carreaux est dans le panier. Le drap est où ?</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1903,8 +1903,8 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Mila a glissé le drap à carreaux dans le panier.
-maman|C'est où, maintenant ?</t>
+          <t>narrateur|Le drap à carreaux est dans le panier.
+maman|Le drap est où ?</t>
         </is>
       </c>
     </row>
@@ -2108,12 +2108,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Le salon a le radiateur tout chaud. Des crochets attendent dans le couloir. La chambre a le lit, comme une scène. Vous jouez où, pour le spectacle ?</t>
+          <t>Le radiateur du salon fait un air tout chaud. Dans le couloir, les crochets attendent, tout hauts. Le lit de la chambre ressemble déjà à une scène. Vous jouez où, pour le spectacle ?</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Le salon a le radiateur tout chaud. Des crochets attendent dans le couloir. La chambre a le lit, comme une scène. Vous jouez où, pour le spectacle ?</t>
+          <t>Le radiateur du salon fait un air tout chaud. Dans le couloir, les crochets attendent, tout hauts. Le lit de la chambre ressemble déjà à une scène. Vous jouez où, pour le spectacle ?</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2272,9 +2272,9 @@
       <c r="AV7" s="2" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>narrateur|Le salon a le radiateur tout chaud.
-narrateur|Des crochets attendent dans le couloir.
-narrateur|La chambre a le lit, comme une scène.
+          <t>narrateur|Le radiateur du salon fait un air tout chaud.
+narrateur|Dans le couloir, les crochets attendent, tout hauts.
+narrateur|Le lit de la chambre ressemble déjà à une scène.
 papa|Vous jouez où, pour le spectacle ?</t>
         </is>
       </c>
@@ -2302,12 +2302,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Mila déplie le drap entre les deux chaises. Le radiateur souffle un air tiède, tout proche. Je vois un nuage sur mes lunettes ! Un rond de buée cache la scène. Le drap retombe, Nino n'a pas vu le bord. Le drap à carreaux attend encore, tout prêt. La chaleur a voilé ses verres, c'est tout. Toi tu vois net, lui un peu flou. On joue comment, alors ? Vous trouvez, tous les deux ?</t>
+          <t>Mila déplie le drap entre les deux chaises. Le radiateur souffle un air tiède, tout proche. Je vois un nuage sur mes lunettes ! Un rond de buée cache la scène. Le drap retombe, Nino n'a pas vu le bord. Le drap à carreaux attend encore, tout prêt. La chaleur a voilé ses verres, c'est tout. Toi tu vois net, lui un peu flou. On joue comment, alors ? La scène est floue, vous faites quoi ?</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Mila déplie le drap entre les deux chaises. Le radiateur souffle un air tiède, tout proche. Je vois un nuage sur mes lunettes ! Un rond de buée cache la scène. Le drap retombe, Nino n'a pas vu le bord. Le drap à carreaux attend encore, tout prêt. La chaleur a voilé ses verres, c'est tout. Toi tu vois net, lui un peu flou. On joue comment, alors ? Vous trouvez, tous les deux ?</t>
+          <t>Mila déplie le drap entre les deux chaises. Le radiateur souffle un air tiède, tout proche. Je vois un nuage sur mes lunettes ! Un rond de buée cache la scène. Le drap retombe, Nino n'a pas vu le bord. Le drap à carreaux attend encore, tout prêt. La chaleur a voilé ses verres, c'est tout. Toi tu vois net, lui un peu flou. On joue comment, alors ? La scène est floue, vous faites quoi ?</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
 maman|La chaleur a voilé ses verres, c'est tout.
 papa|Toi tu vois net, lui un peu flou.
 copain|On joue comment, alors ?
-papa|Vous trouvez, tous les deux ?</t>
+papa|La scène est floue, vous faites quoi ?</t>
         </is>
       </c>
     </row>
@@ -3724,12 +3724,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Mila jette le drap vers le crochet du manteau. Ici, le couloir fait un rideau, Nino. Mes cheveux sont encore lourds du bain. Le drap glisse, accroché à une mèche mouillée. Une goutte tombe sur le carrelage, toc. Ils séchent, tout doux, ce n'est rien. Toi tes nattes tiennent, les siennes gouttent. On peut jouer avec lui ? Vous trouvez, tous les deux ?</t>
+          <t>Mila jette le drap vers le crochet du manteau. Ici, le couloir fait un rideau, Nino. Mes cheveux sont encore lourds du bain. Le drap glisse, accroché à une mèche mouillée. Une goutte tombe sur le carrelage, toc. Ils sèchent, tout doux, ce n'est rien. Toi tes cheveux tiennent, les siens gouttent. On peut jouer avec lui ? Le rideau accroche, vous faites quoi ?</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Mila jette le drap vers le crochet du manteau. Ici, le couloir fait un rideau, Nino. Mes cheveux sont encore lourds du bain. Le drap glisse, accroché à une mèche mouillée. Une goutte tombe sur le carrelage, toc. Ils séchent, tout doux, ce n'est rien. Toi tes nattes tiennent, les siennes gouttent. On peut jouer avec lui ? Vous trouvez, tous les deux ?</t>
+          <t>Mila jette le drap vers le crochet du manteau. Ici, le couloir fait un rideau, Nino. Mes cheveux sont encore lourds du bain. Le drap glisse, accroché à une mèche mouillée. Une goutte tombe sur le carrelage, toc. Ils sèchent, tout doux, ce n'est rien. Toi tes cheveux tiennent, les siens gouttent. On peut jouer avec lui ? Le rideau accroche, vous faites quoi ?</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -3869,10 +3869,10 @@
 copain|Mes cheveux sont encore lourds du bain.
 narrateur|Le drap glisse, accroché à une mèche mouillée.
 narrateur|Une goutte tombe sur le carrelage, toc.
-maman|Ils séchent, tout doux, ce n'est rien.
-papa|Toi tes nattes tiennent, les siennes gouttent.
+maman|Ils sèchent, tout doux, ce n'est rien.
+papa|Toi tes cheveux tiennent, les siens gouttent.
 enfant-f|On peut jouer avec lui ?
-papa|Vous trouvez, tous les deux ?</t>
+papa|Le rideau accroche, vous faites quoi ?</t>
         </is>
       </c>
     </row>
@@ -4095,12 +4095,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>On met la pince plus haut. Mes cheveux restent en bas, alors. Mila clipse le drap plus haut, hors des mèches. Le rideau tient au crochet, tout droit. Les mèches de Nino pendent, libres. Tu peux bouger, maintenant. Le drap ne m'attrape plus. Chacun a sa hauteur, sur le crochet. Les cheveux ont eu leur place.</t>
+          <t>On met la pince plus haut. Mes cheveux restent en bas, alors. Mila attache le drap plus haut, hors des mèches. Le rideau tient au crochet, tout droit. Les mèches de Nino pendent, libres. Tu peux bouger, maintenant. Le drap ne m'attrape plus. Chacun a sa hauteur, sur le crochet. Les cheveux ont eu leur place.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>On met la pince plus haut. Mes cheveux restent en bas, alors. Mila clipse le drap plus haut, hors des mèches. Le rideau tient au crochet, tout droit. Les mèches de Nino pendent, libres. Tu peux bouger, maintenant. Le drap ne m'attrape plus. Chacun a sa hauteur, sur le crochet. Les cheveux ont eu leur place.</t>
+          <t>On met la pince plus haut. Mes cheveux restent en bas, alors. Mila attache le drap plus haut, hors des mèches. Le rideau tient au crochet, tout droit. Les mèches de Nino pendent, libres. Tu peux bouger, maintenant. Le drap ne m'attrape plus. Chacun a sa hauteur, sur le crochet. Les cheveux ont eu leur place.</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4237,7 +4237,7 @@
         <is>
           <t>enfant-f|On met la pince plus haut.
 copain|Mes cheveux restent en bas, alors.
-narrateur|Mila clipse le drap plus haut, hors des mèches.
+narrateur|Mila attache le drap plus haut, hors des mèches.
 narrateur|Le rideau tient au crochet, tout droit.
 narrateur|Les mèches de Nino pendent, libres.
 enfant-f|Tu peux bouger, maintenant.
@@ -4795,12 +4795,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Tu tiens le drap, moi je clips à côté. Mes mains font le crochet, alors. Nino tient le drap à deux mains, sans pince. Le rideau s'ouvre quand Nino recule. Il se ferme quand il avance. C'est toi le rideau vivant ! Et toi le spectacle. Vous jouez avec ce que vous avez. Les cheveux n'ont plus besoin d'être pris.</t>
+          <t>Tu tiens le drap, moi j'attache à côté. Mes mains font le crochet, alors. Nino tient le drap à deux mains, sans pince. Le rideau s'ouvre quand Nino recule. Il se ferme quand il avance. C'est toi le rideau vivant ! Et toi le spectacle. Vous jouez avec ce que vous avez. Les cheveux n'ont plus besoin d'être pris.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Tu tiens le drap, moi je clips à côté. Mes mains font le crochet, alors. Nino tient le drap à deux mains, sans pince. Le rideau s'ouvre quand Nino recule. Il se ferme quand il avance. C'est toi le rideau vivant ! Et toi le spectacle. Vous jouez avec ce que vous avez. Les cheveux n'ont plus besoin d'être pris.</t>
+          <t>Tu tiens le drap, moi j'attache à côté. Mes mains font le crochet, alors. Nino tient le drap à deux mains, sans pince. Le rideau s'ouvre quand Nino recule. Il se ferme quand il avance. C'est toi le rideau vivant ! Et toi le spectacle. Vous jouez avec ce que vous avez. Les cheveux n'ont plus besoin d'être pris.</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -4935,7 +4935,7 @@
       <c r="AV22" s="2" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>enfant-f|Tu tiens le drap, moi je clips à côté.
+          <t>enfant-f|Tu tiens le drap, moi j'attache à côté.
 copain|Mes mains font le crochet, alors.
 narrateur|Nino tient le drap à deux mains, sans pince.
 narrateur|Le rideau s'ouvre quand Nino recule.
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Mila tend le drap au pied du lit. Le lit est notre château, Nino. Mon pull me suit jusqu'aux genoux ! Une manche trop longue emporte un coin du drap. Le drap à carreaux disparaît un instant, sous le tissu. Le pull est un peu grand, c'est tout. Toi tes manches s'arrêtent, les siennes voyagent. On joue comment, alors ? Vous trouvez, tous les deux ?</t>
+          <t>Mila tend le drap au pied du lit. Le lit est notre château, Nino. Mon pull me suit jusqu'aux genoux ! Une manche trop longue emporte un coin du drap. Le drap à carreaux disparaît un instant, sous le tissu. Le pull est un peu grand, c'est tout. Toi tes manches s'arrêtent, les siennes voyagent. On joue comment, alors ? Le pull et le roi, vous faites comment ?</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Mila tend le drap au pied du lit. Le lit est notre château, Nino. Mon pull me suit jusqu'aux genoux ! Une manche trop longue emporte un coin du drap. Le drap à carreaux disparaît un instant, sous le tissu. Le pull est un peu grand, c'est tout. Toi tes manches s'arrêtent, les siennes voyagent. On joue comment, alors ? Vous trouvez, tous les deux ?</t>
+          <t>Mila tend le drap au pied du lit. Le lit est notre château, Nino. Mon pull me suit jusqu'aux genoux ! Une manche trop longue emporte un coin du drap. Le drap à carreaux disparaît un instant, sous le tissu. Le pull est un peu grand, c'est tout. Toi tes manches s'arrêtent, les siennes voyagent. On joue comment, alors ? Le pull et le roi, vous faites comment ?</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5293,7 +5293,7 @@
 maman|Le pull est un peu grand, c'est tout.
 papa|Toi tes manches s'arrêtent, les siennes voyagent.
 copain|On joue comment, alors ?
-papa|Vous trouvez, tous les deux ?</t>
+papa|Le pull et le roi, vous faites comment ?</t>
         </is>
       </c>
     </row>
@@ -6566,12 +6566,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Mila prend d'abord les pinces, toutes froides. Elles cliquettent dans ma paume. Range-les dans ta poche, tout doux. Le métal fait un petit toc contre le tissu. Le drap, ensuite, dans le panier. Elle glisse la marionnette rouge au poignet. Les trois affaires partent ensemble. Nino, tu clips le bord ? J'essaie, mes lunettes glissent un peu. Les pinces d'abord, elles sont prêtes.</t>
+          <t>Mila prend d'abord les pinces, toutes froides. Elles cliquettent dans ma paume. Range-les dans ta poche, tout doux. Le métal fait un petit toc contre le tissu. Le drap, ensuite, dans le panier. Elle glisse la marionnette rouge au poignet. Ils avancent, les affaires avec eux. Nino, tu accroches le bord ? J'essaie, mes lunettes glissent un peu. Les pinces d'abord, elles sont prêtes.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Mila prend d'abord les pinces, toutes froides. Elles cliquettent dans ma paume. Range-les dans ta poche, tout doux. Le métal fait un petit toc contre le tissu. Le drap, ensuite, dans le panier. Elle glisse la marionnette rouge au poignet. Les trois affaires partent ensemble. Nino, tu clips le bord ? J'essaie, mes lunettes glissent un peu. Les pinces d'abord, elles sont prêtes.</t>
+          <t>Mila prend d'abord les pinces, toutes froides. Elles cliquettent dans ma paume. Range-les dans ta poche, tout doux. Le métal fait un petit toc contre le tissu. Le drap, ensuite, dans le panier. Elle glisse la marionnette rouge au poignet. Ils avancent, les affaires avec eux. Nino, tu accroches le bord ? J'essaie, mes lunettes glissent un peu. Les pinces d'abord, elles sont prêtes.</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -6712,8 +6712,8 @@
 narrateur|Le métal fait un petit toc contre le tissu.
 maman|Le drap, ensuite, dans le panier.
 narrateur|Elle glisse la marionnette rouge au poignet.
-narrateur|Les trois affaires partent ensemble.
-enfant-f|Nino, tu clips le bord ?
+narrateur|Ils avancent, les affaires avec eux.
+enfant-f|Nino, tu accroches le bord ?
 copain|J'essaie, mes lunettes glissent un peu.
 maman|Les pinces d'abord, elles sont prêtes.</t>
         </is>
@@ -6742,12 +6742,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Mila a glissé les pinces dans la poche. C'est où, maintenant ?</t>
+          <t>Les pinces sont dans la poche. Les pinces sont où ?</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Mila a glissé les pinces dans la poche. C'est où, maintenant ?</t>
+          <t>Les pinces sont dans la poche. Les pinces sont où ?</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -6898,8 +6898,8 @@
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>narrateur|Mila a glissé les pinces dans la poche.
-maman|C'est où, maintenant ?</t>
+          <t>narrateur|Les pinces sont dans la poche.
+maman|Les pinces sont où ?</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Le salon a le radiateur tout chaud. Des crochets attendent dans le couloir. La chambre a le lit, comme une scène. Vous jouez où, pour le spectacle ?</t>
+          <t>Le radiateur du salon fait un air tout chaud. Dans le couloir, les crochets attendent, tout hauts. Le lit de la chambre ressemble déjà à une scène. Vous jouez où, pour le spectacle ?</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Le salon a le radiateur tout chaud. Des crochets attendent dans le couloir. La chambre a le lit, comme une scène. Vous jouez où, pour le spectacle ?</t>
+          <t>Le radiateur du salon fait un air tout chaud. Dans le couloir, les crochets attendent, tout hauts. Le lit de la chambre ressemble déjà à une scène. Vous jouez où, pour le spectacle ?</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -7267,9 +7267,9 @@
       <c r="AV35" s="2" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>narrateur|Le salon a le radiateur tout chaud.
-narrateur|Des crochets attendent dans le couloir.
-narrateur|La chambre a le lit, comme une scène.
+          <t>narrateur|Le radiateur du salon fait un air tout chaud.
+narrateur|Dans le couloir, les crochets attendent, tout hauts.
+narrateur|Le lit de la chambre ressemble déjà à une scène.
 papa|Vous jouez où, pour le spectacle ?</t>
         </is>
       </c>
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Mila clipse le drap, pince après pince. Le radiateur souffle un air tiède, tout proche. Je vois un nuage sur mes lunettes ! Un rond de buée cache la scène. Une pince tombe : Nino visait à côté. Les pinces attend encore, tout prêt. La chaleur a voilé ses verres, c'est tout. Toi tu vois net, lui un peu flou. On joue comment, alors ? Vous trouvez, tous les deux ?</t>
+          <t>Mila attache le drap, pince après pince. Le radiateur souffle un air tiède, tout proche. Je vois un nuage sur mes lunettes ! Un rond de buée cache la scène. Une pince tombe : Nino visait à côté. Les pinces attend encore, tout prêt. La chaleur a voilé ses verres, c'est tout. Toi tu vois net, lui un peu flou. On joue comment, alors ? La scène est floue, vous faites quoi ?</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Mila clipse le drap, pince après pince. Le radiateur souffle un air tiède, tout proche. Je vois un nuage sur mes lunettes ! Un rond de buée cache la scène. Une pince tombe : Nino visait à côté. Les pinces attend encore, tout prêt. La chaleur a voilé ses verres, c'est tout. Toi tu vois net, lui un peu flou. On joue comment, alors ? Vous trouvez, tous les deux ?</t>
+          <t>Mila attache le drap, pince après pince. Le radiateur souffle un air tiède, tout proche. Je vois un nuage sur mes lunettes ! Un rond de buée cache la scène. Une pince tombe : Nino visait à côté. Les pinces attend encore, tout prêt. La chaleur a voilé ses verres, c'est tout. Toi tu vois net, lui un peu flou. On joue comment, alors ? La scène est floue, vous faites quoi ?</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -7437,7 +7437,7 @@
       <c r="AV36" s="2" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>narrateur|Mila clipse le drap, pince après pince.
+          <t>narrateur|Mila attache le drap, pince après pince.
 narrateur|Le radiateur souffle un air tiède, tout proche.
 copain|Je vois un nuage sur mes lunettes !
 narrateur|Un rond de buée cache la scène.
@@ -7446,7 +7446,7 @@
 maman|La chaleur a voilé ses verres, c'est tout.
 papa|Toi tu vois net, lui un peu flou.
 copain|On joue comment, alors ?
-papa|Vous trouvez, tous les deux ?</t>
+papa|La scène est floue, vous faites quoi ?</t>
         </is>
       </c>
     </row>
@@ -8369,12 +8369,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>On ouvre un peu, papa ? Un doigt de fenêtre, pas plus. L'air froid chasse la buée, tout lent. Les pinces tintent, puis s'apaise le métal. Ça redevient clair ! Le spectacle peut commencer. Nino ajuste ses lunettes, tout net. La chaleur est partie, le jeu reste. Vous avez attendu le verre clair.</t>
+          <t>On ouvre un peu, papa ? Un doigt de fenêtre, pas plus. L'air froid chasse la buée, tout lent. Les pinces tintent, puis le métal se tait. Ça redevient clair ! Le spectacle peut commencer. Nino ajuste ses lunettes, tout net. La chaleur est partie, le jeu reste. Vous avez attendu le verre clair.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>On ouvre un peu, papa ? Un doigt de fenêtre, pas plus. L'air froid chasse la buée, tout lent. Les pinces tintent, puis s'apaise le métal. Ça redevient clair ! Le spectacle peut commencer. Nino ajuste ses lunettes, tout net. La chaleur est partie, le jeu reste. Vous avez attendu le verre clair.</t>
+          <t>On ouvre un peu, papa ? Un doigt de fenêtre, pas plus. L'air froid chasse la buée, tout lent. Les pinces tintent, puis le métal se tait. Ça redevient clair ! Le spectacle peut commencer. Nino ajuste ses lunettes, tout net. La chaleur est partie, le jeu reste. Vous avez attendu le verre clair.</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -8512,7 +8512,7 @@
           <t>enfant-f|On ouvre un peu, papa ?
 papa|Un doigt de fenêtre, pas plus.
 narrateur|L'air froid chasse la buée, tout lent.
-narrateur|Les pinces tintent, puis s'apaise le métal.
+narrateur|Les pinces tintent, puis le métal se tait.
 copain|Ça redevient clair !
 enfant-f|Le spectacle peut commencer.
 narrateur|Nino ajuste ses lunettes, tout net.
@@ -8719,12 +8719,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Mila tend une pince vers le crochet haut. Ici, le couloir fait un rideau, Nino. Mes cheveux sont encore lourds du bain. La pince pince un cheveu, pas le tissu. Une goutte tombe sur le carrelage, toc. Ils séchent, tout doux, ce n'est rien. Toi tes nattes tiennent, les siennes gouttent. On peut jouer avec lui ? Vous trouvez, tous les deux ?</t>
+          <t>Mila tend une pince vers le crochet haut. Ici, le couloir fait un rideau, Nino. Mes cheveux sont encore lourds du bain. La pince pince un cheveu, pas le tissu. Une goutte tombe sur le carrelage, toc. Ils sèchent, tout doux, ce n'est rien. Toi tes cheveux tiennent, les siens gouttent. On peut jouer avec lui ? Le rideau accroche, vous faites quoi ?</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Mila tend une pince vers le crochet haut. Ici, le couloir fait un rideau, Nino. Mes cheveux sont encore lourds du bain. La pince pince un cheveu, pas le tissu. Une goutte tombe sur le carrelage, toc. Ils séchent, tout doux, ce n'est rien. Toi tes nattes tiennent, les siennes gouttent. On peut jouer avec lui ? Vous trouvez, tous les deux ?</t>
+          <t>Mila tend une pince vers le crochet haut. Ici, le couloir fait un rideau, Nino. Mes cheveux sont encore lourds du bain. La pince pince un cheveu, pas le tissu. Une goutte tombe sur le carrelage, toc. Ils sèchent, tout doux, ce n'est rien. Toi tes cheveux tiennent, les siens gouttent. On peut jouer avec lui ? Le rideau accroche, vous faites quoi ?</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -8864,10 +8864,10 @@
 copain|Mes cheveux sont encore lourds du bain.
 narrateur|La pince pince un cheveu, pas le tissu.
 narrateur|Une goutte tombe sur le carrelage, toc.
-maman|Ils séchent, tout doux, ce n'est rien.
-papa|Toi tes nattes tiennent, les siennes gouttent.
+maman|Ils sèchent, tout doux, ce n'est rien.
+papa|Toi tes cheveux tiennent, les siens gouttent.
 enfant-f|On peut jouer avec lui ?
-papa|Vous trouvez, tous les deux ?</t>
+papa|Le rideau accroche, vous faites quoi ?</t>
         </is>
       </c>
     </row>
@@ -9790,12 +9790,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Tu tiens le drap, moi je clips à côté. Mes mains font le crochet, alors. Nino tient le bord, Mila garde les pinces. Le rideau s'ouvre quand Nino recule. Il se ferme quand il avance. C'est toi le rideau vivant ! Et toi le spectacle. Vous jouez avec ce que vous avez. Les cheveux n'ont plus besoin d'être pris.</t>
+          <t>Tu tiens le drap, moi j'attache à côté. Mes mains font le crochet, alors. Nino tient le bord, Mila garde les pinces. Le rideau s'ouvre quand Nino recule. Il se ferme quand il avance. C'est toi le rideau vivant ! Et toi le spectacle. Vous jouez avec ce que vous avez. Les cheveux n'ont plus besoin d'être pris.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Tu tiens le drap, moi je clips à côté. Mes mains font le crochet, alors. Nino tient le bord, Mila garde les pinces. Le rideau s'ouvre quand Nino recule. Il se ferme quand il avance. C'est toi le rideau vivant ! Et toi le spectacle. Vous jouez avec ce que vous avez. Les cheveux n'ont plus besoin d'être pris.</t>
+          <t>Tu tiens le drap, moi j'attache à côté. Mes mains font le crochet, alors. Nino tient le bord, Mila garde les pinces. Le rideau s'ouvre quand Nino recule. Il se ferme quand il avance. C'est toi le rideau vivant ! Et toi le spectacle. Vous jouez avec ce que vous avez. Les cheveux n'ont plus besoin d'être pris.</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -9930,7 +9930,7 @@
       <c r="AV50" s="2" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>enfant-f|Tu tiens le drap, moi je clips à côté.
+          <t>enfant-f|Tu tiens le drap, moi j'attache à côté.
 copain|Mes mains font le crochet, alors.
 narrateur|Nino tient le bord, Mila garde les pinces.
 narrateur|Le rideau s'ouvre quand Nino recule.
@@ -10140,12 +10140,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Mila clipse le drap au bois du lit. Le lit est notre château, Nino. Mon pull me suit jusqu'aux genoux ! Une manche trop longue balaie les pinces. Les pinces disparaît un instant, sous le tissu. Le pull est un peu grand, c'est tout. Toi tes manches s'arrêtent, les siennes voyagent. On joue comment, alors ? Vous trouvez, tous les deux ?</t>
+          <t>Mila attache le drap au bois du lit. Le lit est notre château, Nino. Mon pull me suit jusqu'aux genoux ! Une manche trop longue balaie les pinces. Les pinces disparaît un instant, sous le tissu. Le pull est un peu grand, c'est tout. Toi tes manches s'arrêtent, les siennes voyagent. On joue comment, alors ? Le pull et le roi, vous faites comment ?</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Mila clipse le drap au bois du lit. Le lit est notre château, Nino. Mon pull me suit jusqu'aux genoux ! Une manche trop longue balaie les pinces. Les pinces disparaît un instant, sous le tissu. Le pull est un peu grand, c'est tout. Toi tes manches s'arrêtent, les siennes voyagent. On joue comment, alors ? Vous trouvez, tous les deux ?</t>
+          <t>Mila attache le drap au bois du lit. Le lit est notre château, Nino. Mon pull me suit jusqu'aux genoux ! Une manche trop longue balaie les pinces. Les pinces disparaît un instant, sous le tissu. Le pull est un peu grand, c'est tout. Toi tes manches s'arrêtent, les siennes voyagent. On joue comment, alors ? Le pull et le roi, vous faites comment ?</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -10280,7 +10280,7 @@
       <c r="AV52" s="2" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>narrateur|Mila clipse le drap au bois du lit.
+          <t>narrateur|Mila attache le drap au bois du lit.
 enfant-f|Le lit est notre château, Nino.
 copain|Mon pull me suit jusqu'aux genoux !
 narrateur|Une manche trop longue balaie les pinces.
@@ -10288,7 +10288,7 @@
 maman|Le pull est un peu grand, c'est tout.
 papa|Toi tes manches s'arrêtent, les siennes voyagent.
 copain|On joue comment, alors ?
-papa|Vous trouvez, tous les deux ?</t>
+papa|Le pull et le roi, vous faites comment ?</t>
         </is>
       </c>
     </row>
@@ -10861,12 +10861,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Moi je tiens la marionnette. Moi je fais le rideau, avec le drap. Mila clipse, Nino lève le drap comme un rideau. Les manches trop longues bougent le tissu, seulement. La petite laine reste hors du pull. Le château s'ouvre ! Le roi sort, tout rouge. Chacun a pris sa part, à sa taille. Le lit a tenu le théâtre.</t>
+          <t>Moi je tiens la marionnette. Moi je fais le rideau, avec le drap. Mila attache, Nino lève le drap comme un rideau. Les manches trop longues bougent le tissu, seulement. La petite laine reste hors du pull. Le château s'ouvre ! Le roi sort, tout rouge. Chacun a pris sa part, à sa taille. Le lit a tenu le théâtre.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Moi je tiens la marionnette. Moi je fais le rideau, avec le drap. Mila clipse, Nino lève le drap comme un rideau. Les manches trop longues bougent le tissu, seulement. La petite laine reste hors du pull. Le château s'ouvre ! Le roi sort, tout rouge. Chacun a pris sa part, à sa taille. Le lit a tenu le théâtre.</t>
+          <t>Moi je tiens la marionnette. Moi je fais le rideau, avec le drap. Mila attache, Nino lève le drap comme un rideau. Les manches trop longues bougent le tissu, seulement. La petite laine reste hors du pull. Le château s'ouvre ! Le roi sort, tout rouge. Chacun a pris sa part, à sa taille. Le lit a tenu le théâtre.</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -11003,7 +11003,7 @@
         <is>
           <t>enfant-f|Moi je tiens la marionnette.
 copain|Moi je fais le rideau, avec le drap.
-narrateur|Mila clipse, Nino lève le drap comme un rideau.
+narrateur|Mila attache, Nino lève le drap comme un rideau.
 narrateur|Les manches trop longues bougent le tissu, seulement.
 narrateur|La petite laine reste hors du pull.
 copain|Le château s'ouvre !
@@ -11561,12 +11561,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Mila enfile d'abord la marionnette rouge. Elle marche déjà sur ma main. Garde-la au poignet, comme un secret. La laine rouge chatouille la peau. Le drap et les pinces, avec vous. Il les pose près du panier. Les trois affaires partent ensemble. Nino, elle te salue ! Bonjour, petite laine. La marionnette d'abord, elle est prête.</t>
+          <t>Mila enfile d'abord la marionnette rouge. Elle marche déjà sur ma main. Garde-la au poignet, comme un secret. La laine rouge chatouille la peau. Le drap et les pinces, avec vous. Il les pose près du panier. Le spectacle quitte le coffre, enfin. Nino, elle te salue ! Bonjour, petite laine. La marionnette d'abord, elle est prête.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>Mila enfile d'abord la marionnette rouge. Elle marche déjà sur ma main. Garde-la au poignet, comme un secret. La laine rouge chatouille la peau. Le drap et les pinces, avec vous. Il les pose près du panier. Les trois affaires partent ensemble. Nino, elle te salue ! Bonjour, petite laine. La marionnette d'abord, elle est prête.</t>
+          <t>Mila enfile d'abord la marionnette rouge. Elle marche déjà sur ma main. Garde-la au poignet, comme un secret. La laine rouge chatouille la peau. Le drap et les pinces, avec vous. Il les pose près du panier. Le spectacle quitte le coffre, enfin. Nino, elle te salue ! Bonjour, petite laine. La marionnette d'abord, elle est prête.</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -11707,7 +11707,7 @@
 narrateur|La laine rouge chatouille la peau.
 papa|Le drap et les pinces, avec vous.
 narrateur|Il les pose près du panier.
-narrateur|Les trois affaires partent ensemble.
+narrateur|Le spectacle quitte le coffre, enfin.
 enfant-f|Nino, elle te salue !
 copain|Bonjour, petite laine.
 papa|La marionnette d'abord, elle est prête.</t>
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Mila a glissé la marionnette rouge au poignet. C'est où, maintenant ?</t>
+          <t>La marionnette rouge est au poignet. La marionnette est où ?</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>Mila a glissé la marionnette rouge au poignet. C'est où, maintenant ?</t>
+          <t>La marionnette rouge est au poignet. La marionnette est où ?</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -11893,8 +11893,8 @@
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>narrateur|Mila a glissé la marionnette rouge au poignet.
-maman|C'est où, maintenant ?</t>
+          <t>narrateur|La marionnette rouge est au poignet.
+maman|La marionnette est où ?</t>
         </is>
       </c>
     </row>
@@ -12098,12 +12098,12 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Le salon a le radiateur tout chaud. Des crochets attendent dans le couloir. La chambre a le lit, comme une scène. Vous jouez où, pour le spectacle ?</t>
+          <t>Le radiateur du salon fait un air tout chaud. Dans le couloir, les crochets attendent, tout hauts. Le lit de la chambre ressemble déjà à une scène. Vous jouez où, pour le spectacle ?</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>Le salon a le radiateur tout chaud. Des crochets attendent dans le couloir. La chambre a le lit, comme une scène. Vous jouez où, pour le spectacle ?</t>
+          <t>Le radiateur du salon fait un air tout chaud. Dans le couloir, les crochets attendent, tout hauts. Le lit de la chambre ressemble déjà à une scène. Vous jouez où, pour le spectacle ?</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -12262,9 +12262,9 @@
       <c r="AV63" s="2" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>narrateur|Le salon a le radiateur tout chaud.
-narrateur|Des crochets attendent dans le couloir.
-narrateur|La chambre a le lit, comme une scène.
+          <t>narrateur|Le radiateur du salon fait un air tout chaud.
+narrateur|Dans le couloir, les crochets attendent, tout hauts.
+narrateur|Le lit de la chambre ressemble déjà à une scène.
 papa|Vous jouez où, pour le spectacle ?</t>
         </is>
       </c>
@@ -12292,12 +12292,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>La marionnette grimpe le dossier d'une chaise. Le radiateur souffle un air tiède, tout proche. Je vois un nuage sur mes lunettes ! Un rond de buée cache la scène. La marionnette salue, Nino la cherche trop bas. La marionnette rouge attend encore, tout prêt. La chaleur a voilé ses verres, c'est tout. Toi tu vois net, lui un peu flou. On joue comment, alors ? Vous trouvez, tous les deux ?</t>
+          <t>La marionnette grimpe le dossier d'une chaise. Le radiateur souffle un air tiède, tout proche. Je vois un nuage sur mes lunettes ! Un rond de buée cache la scène. La marionnette salue, Nino la cherche trop bas. La marionnette rouge attend encore, tout prêt. La chaleur a voilé ses verres, c'est tout. Toi tu vois net, lui un peu flou. On joue comment, alors ? La scène est floue, vous faites quoi ?</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>La marionnette grimpe le dossier d'une chaise. Le radiateur souffle un air tiède, tout proche. Je vois un nuage sur mes lunettes ! Un rond de buée cache la scène. La marionnette salue, Nino la cherche trop bas. La marionnette rouge attend encore, tout prêt. La chaleur a voilé ses verres, c'est tout. Toi tu vois net, lui un peu flou. On joue comment, alors ? Vous trouvez, tous les deux ?</t>
+          <t>La marionnette grimpe le dossier d'une chaise. Le radiateur souffle un air tiède, tout proche. Je vois un nuage sur mes lunettes ! Un rond de buée cache la scène. La marionnette salue, Nino la cherche trop bas. La marionnette rouge attend encore, tout prêt. La chaleur a voilé ses verres, c'est tout. Toi tu vois net, lui un peu flou. On joue comment, alors ? La scène est floue, vous faites quoi ?</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -12441,7 +12441,7 @@
 maman|La chaleur a voilé ses verres, c'est tout.
 papa|Toi tu vois net, lui un peu flou.
 copain|On joue comment, alors ?
-papa|Vous trouvez, tous les deux ?</t>
+papa|La scène est floue, vous faites quoi ?</t>
         </is>
       </c>
     </row>
@@ -13714,12 +13714,12 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>La marionnette tire le drap, vers le crochet. Ici, le couloir fait un rideau, Nino. Mes cheveux sont encore lourds du bain. La laine rouge s'emmêle à une mèche encore humide. Une goutte tombe sur le carrelage, toc. Ils séchent, tout doux, ce n'est rien. Toi tes nattes tiennent, les siennes gouttent. On peut jouer avec lui ? Vous trouvez, tous les deux ?</t>
+          <t>La marionnette tire le drap, vers le crochet. Ici, le couloir fait un rideau, Nino. Mes cheveux sont encore lourds du bain. La laine rouge s'emmêle à une mèche encore humide. Une goutte tombe sur le carrelage, toc. Ils sèchent, tout doux, ce n'est rien. Toi tes cheveux tiennent, les siens gouttent. On peut jouer avec lui ? Le rideau accroche, vous faites quoi ?</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>La marionnette tire le drap, vers le crochet. Ici, le couloir fait un rideau, Nino. Mes cheveux sont encore lourds du bain. La laine rouge s'emmêle à une mèche encore humide. Une goutte tombe sur le carrelage, toc. Ils séchent, tout doux, ce n'est rien. Toi tes nattes tiennent, les siennes gouttent. On peut jouer avec lui ? Vous trouvez, tous les deux ?</t>
+          <t>La marionnette tire le drap, vers le crochet. Ici, le couloir fait un rideau, Nino. Mes cheveux sont encore lourds du bain. La laine rouge s'emmêle à une mèche encore humide. Une goutte tombe sur le carrelage, toc. Ils sèchent, tout doux, ce n'est rien. Toi tes cheveux tiennent, les siens gouttent. On peut jouer avec lui ? Le rideau accroche, vous faites quoi ?</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -13859,10 +13859,10 @@
 copain|Mes cheveux sont encore lourds du bain.
 narrateur|La laine rouge s'emmêle à une mèche encore humide.
 narrateur|Une goutte tombe sur le carrelage, toc.
-maman|Ils séchent, tout doux, ce n'est rien.
-papa|Toi tes nattes tiennent, les siennes gouttent.
+maman|Ils sèchent, tout doux, ce n'est rien.
+papa|Toi tes cheveux tiennent, les siens gouttent.
 enfant-f|On peut jouer avec lui ?
-papa|Vous trouvez, tous les deux ?</t>
+papa|Le rideau accroche, vous faites quoi ?</t>
         </is>
       </c>
     </row>
@@ -14785,12 +14785,12 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Tu tiens le drap, moi je clips à côté. Mes mains font le crochet, alors. Nino tient le drap, la marionnette salue. Le rideau s'ouvre quand Nino recule. Il se ferme quand il avance. C'est toi le rideau vivant ! Et toi le spectacle. Vous jouez avec ce que vous avez. Les cheveux n'ont plus besoin d'être pris.</t>
+          <t>Tu tiens le drap, moi j'attache à côté. Mes mains font le crochet, alors. Nino tient le drap, la marionnette salue. Le rideau s'ouvre quand Nino recule. Il se ferme quand il avance. C'est toi le rideau vivant ! Et toi le spectacle. Vous jouez avec ce que vous avez. Les cheveux n'ont plus besoin d'être pris.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>Tu tiens le drap, moi je clips à côté. Mes mains font le crochet, alors. Nino tient le drap, la marionnette salue. Le rideau s'ouvre quand Nino recule. Il se ferme quand il avance. C'est toi le rideau vivant ! Et toi le spectacle. Vous jouez avec ce que vous avez. Les cheveux n'ont plus besoin d'être pris.</t>
+          <t>Tu tiens le drap, moi j'attache à côté. Mes mains font le crochet, alors. Nino tient le drap, la marionnette salue. Le rideau s'ouvre quand Nino recule. Il se ferme quand il avance. C'est toi le rideau vivant ! Et toi le spectacle. Vous jouez avec ce que vous avez. Les cheveux n'ont plus besoin d'être pris.</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -14925,7 +14925,7 @@
       <c r="AV78" s="2" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>enfant-f|Tu tiens le drap, moi je clips à côté.
+          <t>enfant-f|Tu tiens le drap, moi j'attache à côté.
 copain|Mes mains font le crochet, alors.
 narrateur|Nino tient le drap, la marionnette salue.
 narrateur|Le rideau s'ouvre quand Nino recule.
@@ -15135,12 +15135,12 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>La marionnette se cache sous l'oreiller. Le lit est notre château, Nino. Mon pull me suit jusqu'aux genoux ! Une manche trop longue avale la marionnette. La marionnette rouge disparaît un instant, sous le tissu. Le pull est un peu grand, c'est tout. Toi tes manches s'arrêtent, les siennes voyagent. On joue comment, alors ? Vous trouvez, tous les deux ?</t>
+          <t>La marionnette se cache sous l'oreiller. Le lit est notre château, Nino. Mon pull me suit jusqu'aux genoux ! Une manche trop longue avale la marionnette. La marionnette rouge disparaît un instant, sous le tissu. Le pull est un peu grand, c'est tout. Toi tes manches s'arrêtent, les siennes voyagent. On joue comment, alors ? Le pull et le roi, vous faites comment ?</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>La marionnette se cache sous l'oreiller. Le lit est notre château, Nino. Mon pull me suit jusqu'aux genoux ! Une manche trop longue avale la marionnette. La marionnette rouge disparaît un instant, sous le tissu. Le pull est un peu grand, c'est tout. Toi tes manches s'arrêtent, les siennes voyagent. On joue comment, alors ? Vous trouvez, tous les deux ?</t>
+          <t>La marionnette se cache sous l'oreiller. Le lit est notre château, Nino. Mon pull me suit jusqu'aux genoux ! Une manche trop longue avale la marionnette. La marionnette rouge disparaît un instant, sous le tissu. Le pull est un peu grand, c'est tout. Toi tes manches s'arrêtent, les siennes voyagent. On joue comment, alors ? Le pull et le roi, vous faites comment ?</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -15283,7 +15283,7 @@
 maman|Le pull est un peu grand, c'est tout.
 papa|Toi tes manches s'arrêtent, les siennes voyagent.
 copain|On joue comment, alors ?
-papa|Vous trouvez, tous les deux ?</t>
+papa|Le pull et le roi, vous faites comment ?</t>
         </is>
       </c>
     </row>
@@ -16550,7 +16550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A14"/>
+  <dimension ref="A1:A15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16649,6 +16649,13 @@
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
